--- a/MappingGuides/mapping/guides/MappingGuide_PDS002MI_ProductStructure.xlsx
+++ b/MappingGuides/mapping/guides/MappingGuide_PDS002MI_ProductStructure.xlsx
@@ -935,12 +935,7 @@
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.</t>
-        </is>
-      </c>
+      <c r="AA3" s="2" t="inlineStr"/>
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1039,14 +1034,7 @@
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).</t>
-        </is>
-      </c>
+      <c r="AA4" s="2" t="inlineStr"/>
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1153,13 +1141,7 @@
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr"/>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product number.
-For a product structure with a product structure class type of 00-'Standard' (i.e. discrete items), the product number is the same as the item number manufactured (the output from the manufacturing order) and is always used together with structures to describe what a product consists of and how it is manufactured.
-There are scenarios where each process is created as a product number on (PDS001) to serve as a placeholder for product structure class types other than 00-'Standard'. In the cases where the product structure class type is Formula product structure, Routing product structure, Bulk item product structure, Packaging material product structure, or Packaged item product structure, the Product number field is used to identify a process required for the manufacture of the ultimate product number.</t>
-        </is>
-      </c>
+      <c r="AA5" s="2" t="inlineStr"/>
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1262,11 +1244,7 @@
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr"/>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a product structure type. You can define more than one product structure per product and facility.</t>
-        </is>
-      </c>
+      <c r="AA6" s="2" t="inlineStr"/>
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -1377,14 +1355,7 @@
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates an operation number, which forms a unique ID for an operation when combined with a product number.
-For each operation number, enter the work center where the operation should be performed along with information such as operation name, run time and setup time.
-The operation number also indicates the order in which operations should be performed for a product.
-When an operation number has been entered on a material line in a product structure, it refers to the operation in which the material should first be used.</t>
-        </is>
-      </c>
+      <c r="AA7" s="2" t="inlineStr"/>
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr"/>
@@ -1475,12 +1446,7 @@
       <c r="X8" s="2" t="inlineStr"/>
       <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr"/>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the sequence number.
-The number is a part of the key identity for the material records of each product structure (BoM) and order. The sequence number is entered manually and is four positions long.</t>
-        </is>
-      </c>
+      <c r="AA8" s="2" t="inlineStr"/>
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr"/>
@@ -1769,14 +1735,7 @@
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr"/>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a work center, which is a resource in which labor operations are performed.
-A work center can consist of one or more exchangeable machines or people. The work center can also be external and is then defined as a subcontract group.
-The work center is considered the smallest unit for capacity and load planning, unless M3 Scheduling Workbench (SWB) is active. In that case, planning is carried out for each work center resource.
-Work centers are defined in (PDS010).</t>
-        </is>
-      </c>
+      <c r="AA11" s="2" t="inlineStr"/>
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
@@ -2145,17 +2104,8 @@
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how this operation is processed if it is part of a phantom routing.</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>1: Added as a new operation
-2: Accumulation of run time.</t>
-        </is>
-      </c>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr"/>
       <c r="AE15" s="2" t="inlineStr"/>
@@ -2241,12 +2191,7 @@
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the unique ID of a document. It can be entered manually, generated from a number series or created as a combination of different IDs.
-How the ID is created for each document type is specified in (CRS236).</t>
-        </is>
-      </c>
+      <c r="AA16" s="2" t="inlineStr"/>
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
@@ -2337,11 +2282,7 @@
       <c r="X17" s="2" t="inlineStr"/>
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if the run time entered should apply as total production time regardless of the quantity.</t>
-        </is>
-      </c>
+      <c r="AA17" s="2" t="inlineStr"/>
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr"/>
@@ -2525,12 +2466,7 @@
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the time associated with a setup procedure performed while the machine is running. It is not included in the calculation of load and lead time.
-The external setup time is used as a cost driver in the product costing.</t>
-        </is>
-      </c>
+      <c r="AA19" s="2" t="inlineStr"/>
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr"/>
@@ -3371,12 +3307,7 @@
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr"/>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a time reference, which makes it possible to group operations for greater efficiency.
-The value is proposed by default when entering operations in the current work center.</t>
-        </is>
-      </c>
+      <c r="AA28" s="2" t="inlineStr"/>
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
@@ -3463,13 +3394,7 @@
       <c r="X29" s="2" t="inlineStr"/>
       <c r="Y29" s="2" t="inlineStr"/>
       <c r="Z29" s="2" t="inlineStr"/>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the pay element.
-The pay element describes the type of wage assigned to a task, for example setup work, overtime. Pay elements must be entered when a connection to Payroll &amp; Benefits (PAY) exists.
-The pay element is entered for the operation record. When entering operations, the pay element from the work center is displayed by default. The pay element that has been entered for each operation record may be changed when reporting operations.</t>
-        </is>
-      </c>
+      <c r="AA29" s="2" t="inlineStr"/>
       <c r="AB29" s="2" t="inlineStr"/>
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr"/>
@@ -3556,11 +3481,7 @@
       <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="inlineStr"/>
       <c r="Z30" s="2" t="inlineStr"/>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the weight in kilos before the current operation was performed.</t>
-        </is>
-      </c>
+      <c r="AA30" s="2" t="inlineStr"/>
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr"/>
@@ -3647,11 +3568,7 @@
       <c r="X31" s="2" t="inlineStr"/>
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr"/>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the volume of the operation, which can be used as a cost driver in the product costing.</t>
-        </is>
-      </c>
+      <c r="AA31" s="2" t="inlineStr"/>
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr"/>
@@ -3738,12 +3655,7 @@
       <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr"/>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a multiplication factor used in product costing.
-The purpose of this factor is to neutralize any differences in unit for different products.</t>
-        </is>
-      </c>
+      <c r="AA32" s="2" t="inlineStr"/>
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr"/>
@@ -3830,12 +3742,7 @@
       <c r="X33" s="2" t="inlineStr"/>
       <c r="Y33" s="2" t="inlineStr"/>
       <c r="Z33" s="2" t="inlineStr"/>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the multiplier used during product costing.
-The multiplier can be used for either a volume-based or order-based cost driver.</t>
-        </is>
-      </c>
+      <c r="AA33" s="2" t="inlineStr"/>
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr"/>
@@ -3926,11 +3833,7 @@
       <c r="X34" s="2" t="inlineStr"/>
       <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr"/>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the skill required to perform an operation. This skill is defined using a two-digit (predefined) code.</t>
-        </is>
-      </c>
+      <c r="AA34" s="2" t="inlineStr"/>
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
@@ -4021,11 +3924,7 @@
       <c r="X35" s="2" t="inlineStr"/>
       <c r="Y35" s="2" t="inlineStr"/>
       <c r="Z35" s="2" t="inlineStr"/>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the skill required to perform an inspection. This skill is defined using a two-digit (predefined) code.</t>
-        </is>
-      </c>
+      <c r="AA35" s="2" t="inlineStr"/>
       <c r="AB35" s="2" t="inlineStr"/>
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr"/>
@@ -4213,11 +4112,7 @@
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr"/>
       <c r="Z37" s="2" t="inlineStr"/>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the share, as a percentage, that this variant stands for in relation to the total quantity of variants entered for the product number. The information is used for requirement calculations.</t>
-        </is>
-      </c>
+      <c r="AA37" s="2" t="inlineStr"/>
       <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr"/>
@@ -4316,14 +4211,7 @@
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr"/>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to enter standard code for each material and/or operation. The code controls whether materials and operations should be considered in estimate, requirements calculation and lead time calculation of the product, according to:
-Items that do not contain variants of materials or alternative operations normally have standard code 1 for all structure lines. Also items that contain variants of materials or operations normally have standard code 1 but combined with option percentage. Option percentage indicates how much of the materials and operations should be considered in estimate, requirements calculation and lead time calculation.
-For products with operations that are controlled by alternative routing (one 'standard' alternative routing must exists in PDS001) and record exists in PDS008, the operations will be included in the estimate, requirements and lead time calculation regardless of the option selected in this code. Otherwise, the option to include the operations in the calculation is still determined by this code.
-For products with operations that have record in PDS003, the operations will be included in the estimate, requirements and lead time calculation regardless of the option selected in this code. Otherwise, the option to include the operations in the calculation is still determined by this code.</t>
-        </is>
-      </c>
+      <c r="AA38" s="2" t="inlineStr"/>
       <c r="AB38" s="2" t="inlineStr"/>
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr"/>
@@ -4497,12 +4385,7 @@
       <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
       <c r="Z40" s="2" t="inlineStr"/>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of labor tickets to be printed per operation. The number is determined per product record, per unique operation and by the labor ticket multiplier.
-The two values are multiplied to give the total number of labor tickets per operation.</t>
-        </is>
-      </c>
+      <c r="AA40" s="2" t="inlineStr"/>
       <c r="AB40" s="2" t="inlineStr"/>
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr"/>
@@ -4593,13 +4476,7 @@
       <c r="X41" s="2" t="inlineStr"/>
       <c r="Y41" s="2" t="inlineStr"/>
       <c r="Z41" s="2" t="inlineStr"/>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the transit value, entered in the applicable unit for the operation's work center.
-The value represents the transit time from one operation to the next, and can be either positive or negative. A negative value indicates an overlap.
-The value is used when calculating manufacturing lead times for product structures and manufacturing orders.</t>
-        </is>
-      </c>
+      <c r="AA41" s="2" t="inlineStr"/>
       <c r="AB41" s="2" t="inlineStr"/>
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr"/>
@@ -4686,12 +4563,7 @@
       <c r="X42" s="2" t="inlineStr"/>
       <c r="Y42" s="2" t="inlineStr"/>
       <c r="Z42" s="2" t="inlineStr"/>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of workdays an operation must be started before the finish date of a product.
-The value is calculated by the system in the lead time calculation and is only used for the lead time calculation of a product structure. The calculation is performed for each order quantity of the product and is based on the nominal capacity for each work center and on the transport time table.</t>
-        </is>
-      </c>
+      <c r="AA42" s="2" t="inlineStr"/>
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr"/>
@@ -4778,12 +4650,7 @@
       <c r="X43" s="2" t="inlineStr"/>
       <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr"/>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of days the operation is in progress; that is, the difference between the planned finish date and planned start date.
-Production days are calculated automatically for all operations except subcontract operations. These are entered manually, and refer to the subcontract operation's lead time, which is always independent of volume.</t>
-        </is>
-      </c>
+      <c r="AA43" s="2" t="inlineStr"/>
       <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr"/>
@@ -4870,13 +4737,7 @@
       <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr"/>
       <c r="Z44" s="2" t="inlineStr"/>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates setup scrap.
-Setup scrap is entered for each labor operation and is an extra material quantity that will be used for the setup work.
-The size of this quantity depends on the batch size and affects the material reservations for all materials included in each operation. Furthermore, the setup scrap is considered in the load planning and the product costing.</t>
-        </is>
-      </c>
+      <c r="AA44" s="2" t="inlineStr"/>
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr"/>
@@ -5054,11 +4915,7 @@
       <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr"/>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the correct delivery address for the purchase order line, that is the next subcontractor's address.</t>
-        </is>
-      </c>
+      <c r="AA46" s="2" t="inlineStr"/>
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr"/>
@@ -5141,12 +4998,7 @@
       <c r="X47" s="2" t="inlineStr"/>
       <c r="Y47" s="2" t="inlineStr"/>
       <c r="Z47" s="2" t="inlineStr"/>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the unique identity for a formula. Together with the result identity, the formula is used by the configurator to calculate the operation's run time.
-The formula will always give the answer in hours. This makes it possible to use the formula for different operations using different units.</t>
-        </is>
-      </c>
+      <c r="AA47" s="2" t="inlineStr"/>
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr"/>
@@ -5229,13 +5081,7 @@
       <c r="X48" s="2" t="inlineStr"/>
       <c r="Y48" s="2" t="inlineStr"/>
       <c r="Z48" s="2" t="inlineStr"/>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates which result ID for the specified formula is to be used to update the run time. It can only be entered in combination with the formula ID.
-If only a formula ID is specified, the system will use the result last calculated in the formula.
-If either a formula or result ID is specified, the system will use the run time specified for the operation.</t>
-        </is>
-      </c>
+      <c r="AA48" s="2" t="inlineStr"/>
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr"/>
@@ -5314,12 +5160,7 @@
       <c r="X49" s="2" t="inlineStr"/>
       <c r="Y49" s="2" t="inlineStr"/>
       <c r="Z49" s="2" t="inlineStr"/>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the maximum duration an operation can have when it is scheduled, expressed as a percentage (compared to the theoretical operation time).
-If the duration of an operation (time from start to finish) exceeds the max duration, the operation is rescheduled.</t>
-        </is>
-      </c>
+      <c r="AA49" s="2" t="inlineStr"/>
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr"/>
@@ -5402,12 +5243,7 @@
       <c r="X50" s="2" t="inlineStr"/>
       <c r="Y50" s="2" t="inlineStr"/>
       <c r="Z50" s="2" t="inlineStr"/>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to prevent overload from being created for the bottleneck operation when calculating start and/or finish times for an order.
-If M3 SWB is activated for the facility, use finite capacity planning with appropriate capacity levels (on (PDS010/K)) for all work center resources (type 6). Then you can set the work centers that use finite capacity planning per simulation step.</t>
-        </is>
-      </c>
+      <c r="AA50" s="2" t="inlineStr"/>
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr"/>
@@ -5490,18 +5326,8 @@
       <c r="X51" s="2" t="inlineStr"/>
       <c r="Y51" s="2" t="inlineStr"/>
       <c r="Z51" s="2" t="inlineStr"/>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how orders for subcontract operations should be created.</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr">
-        <is>
-          <t>Blank: No purchase order or requisition order is created.
-1: Purchase order and requisition order are created.
-2: Only a requisition order is created.</t>
-        </is>
-      </c>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr"/>
       <c r="AE51" s="2" t="inlineStr"/>
@@ -5583,11 +5409,7 @@
       <c r="X52" s="2" t="inlineStr"/>
       <c r="Y52" s="2" t="inlineStr"/>
       <c r="Z52" s="2" t="inlineStr"/>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if (PMS050) for manufacturing orders or (MOS050) for work orders should be automatically displayed when reporting the last operation in an order.</t>
-        </is>
-      </c>
+      <c r="AA52" s="2" t="inlineStr"/>
       <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr"/>
@@ -5674,19 +5496,8 @@
       <c r="X53" s="2" t="inlineStr"/>
       <c r="Y53" s="2" t="inlineStr"/>
       <c r="Z53" s="2" t="inlineStr"/>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether an operation planned for this work center should be reported automatically.</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>0: No
-1: Yes, according to reported quantity from the next controlling operation
-2: Controlling operation.
-3: Yes, based on reported quantity</t>
-        </is>
-      </c>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr"/>
       <c r="AE53" s="2" t="inlineStr"/>
@@ -5768,12 +5579,7 @@
       <c r="X54" s="2" t="inlineStr"/>
       <c r="Y54" s="2" t="inlineStr"/>
       <c r="Z54" s="2" t="inlineStr"/>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to specify whether all subassemblies (suborders) must be finished before the start date of this operation.
-If the check box is selected, a warning is issued if the finish date for the subassembly (suborder) is later than the start date of the assembly operation. The warning is issued in (MOS110).</t>
-        </is>
-      </c>
+      <c r="AA54" s="2" t="inlineStr"/>
       <c r="AB54" s="2" t="inlineStr"/>
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr"/>
@@ -5848,12 +5654,7 @@
       <c r="X55" s="2" t="inlineStr"/>
       <c r="Y55" s="2" t="inlineStr"/>
       <c r="Z55" s="2" t="inlineStr"/>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the next APP operation number, which is used to identify the next operation in the routing, that is to say the operation that follows the current operation. You can use the next operation number for defining parallel and divergent operations in the routing.
-If the next operation number is zero, then by default the operation with the next highest operation number will be used as the next operation.</t>
-        </is>
-      </c>
+      <c r="AA55" s="2" t="inlineStr"/>
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr"/>
@@ -5928,12 +5729,7 @@
       <c r="X56" s="2" t="inlineStr"/>
       <c r="Y56" s="2" t="inlineStr"/>
       <c r="Z56" s="2" t="inlineStr"/>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the M3 SWB operation number. Together with the operation number, the M3 SWB operation number defines an operation uniquely within an order. It controls the sequence in which the operations are scheduled in M3 SWB. The operations are scheduled in ascending order.
-The M3 SWB operation number is also used when defining parallel operations. Parallel operations always involve one operation assigned as primary operation and one or more secondary operations. Important: Secondary operations must have operation numbers that are less than the operation number of the primary operation.</t>
-        </is>
-      </c>
+      <c r="AA56" s="2" t="inlineStr"/>
       <c r="AB56" s="2" t="inlineStr"/>
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr"/>
@@ -6008,24 +5804,8 @@
       <c r="X57" s="2" t="inlineStr"/>
       <c r="Y57" s="2" t="inlineStr"/>
       <c r="Z57" s="2" t="inlineStr"/>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a code that determines whether a secondary operation occurs at the same time as a primary operation. The secondary operation can be a setup person, an operator, a cleaning process, and so on.
-Overlap codes 11 through 15 define the rules for scheduling the secondary operation in reference to the primary operation.</t>
-        </is>
-      </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>0: No overlap.
-10: From the start of the primary operation. The start time for the secondary operation is forced to be the same as the start time for the primary operation plus the overlap base.
-11: The start and end are the same as for the primary operation. Acts like overlap code 10 except that the end time for the secondary operation is always set to the end time of the primary operation regardless of the scheduled operation times.
-12: From the end of the primary operation. The end time for the secondary operation is forced to be the same as the end time for the primary operation minus the overlap base.
-13: In between the start and end of the primary operation. The start time of the secondary operation is placed in between the start time for the primary operation (plus the overlap base) and the end time for the primary operation.
-14: Placeholder total order. The secondary operation covers all the operations for the order, that is, from the start time of the first operation to the end time of the last operation. The operation time defines the minimum elapsed time and the overlap base defines the maximum elapsed time. Elapsed time is calculated on a continuous time scale, and therefore the shift pattern lines and non-working days are not taken into account.
-15: Placeholder adjustment operation. The secondary operation covers two consecutive operations, the primary operation and the previous operation (lower operation number). As with overlap code 14, the operation time and overlap base define the minimum and maximum elapsed time, respectively. In this case the definitions only apply to the two operations involved.
-16: Fill-up constraint. The entire load of the secondary operation is planned on the planned end date of the primary operation.</t>
-        </is>
-      </c>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
       <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr"/>
       <c r="AE57" s="2" t="inlineStr"/>
@@ -6099,28 +5879,8 @@
       <c r="X58" s="2" t="inlineStr"/>
       <c r="Y58" s="2" t="inlineStr"/>
       <c r="Z58" s="2" t="inlineStr"/>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the queue/transit time is reported to the next work center in the operation chain. The queue/transit type is specified per work center.</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>Blank: Not used.
-1: Queue/transit days. Positive number of days indicates the planned queue/transit time after operation. Negative number of days means an overlap exists, for example operation 2 is planned to start when there are still days remaining in operation 1.
-2: Hours. Positive number of hours indicates the planned queue/transit time after operation. Negative number of hours means overlap exists, for example operation 2 is planned to start when there are still hours remaining in operation 1.
-3: Percentage. Entered as a positive value and always indicates an overlap. Operation 2 starts when the entered percentage of the time for operation 1 remains.
-4: Quantity. Entered as a positive value and always indicates an overlap. Operation 2 starts when the entered quantity has been manufactured by operation 1.
-Blank: No overlap.
-1: Not used.
-2: Hours. A number of hours counted backwards form the planned end time of the operation at which production may start at the next operation. This number must be positive and always indicates an overlap.
-3: Not used.
-4: Quantity. Entered as a positive value and always indicates an overlap. When the entered quantity has been manufactured in the current operation, the next operation may start.
-5: Number of batches. The current operation is split into a number of batches defined in the overlap base field. The next operation can start when the first batch for the current operation is finished. M3 SWB ensures that the last batch starts in the next operation only when it has been finished in the current operation.
-6: Minimum elapsed production time. The next operation will start when the current operation has run for the entered number of hours. M3 SWB ensures that the quantity produced within the minimum elapsed production time is not started in the next operation until it has been finished in the current operation.
-7: Minimum quantity produced. The next operation will start when the entered quantity has been produced in the current operation. M3 SWB ensures that the last quantity is not started in the next operation until it has been finished in the current operation.</t>
-        </is>
-      </c>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr"/>
       <c r="AE58" s="2" t="inlineStr"/>
@@ -6194,11 +5954,7 @@
       <c r="X59" s="2" t="inlineStr"/>
       <c r="Y59" s="2" t="inlineStr"/>
       <c r="Z59" s="2" t="inlineStr"/>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the resource restriction, which is used to control the process of selecting resources within a work center. A minimum and maximum restriction are defined for the resource. If the restriction defined for the operation is outside the interval formed by the minimum and maximum restrictions, then the operation will not be scheduled for this resource.</t>
-        </is>
-      </c>
+      <c r="AA59" s="2" t="inlineStr"/>
       <c r="AB59" s="2" t="inlineStr"/>
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr"/>
@@ -6273,21 +6029,8 @@
       <c r="X60" s="2" t="inlineStr"/>
       <c r="Y60" s="2" t="inlineStr"/>
       <c r="Z60" s="2" t="inlineStr"/>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how to split an operation onto several machines allowing you to finish it earlier, thus reducing the order lead-time.
-The split method determines in what way an operation is to be split when transferred to the M3 SWB / M3 PWB client.</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>0: No split.
-5: Split by quantity (integers).
-6: Split by quantity (reals).
-7: Split by quantity.
-8: Split by number of operations.</t>
-        </is>
-      </c>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr"/>
       <c r="AE60" s="2" t="inlineStr"/>
@@ -6361,11 +6104,7 @@
       <c r="X61" s="2" t="inlineStr"/>
       <c r="Y61" s="2" t="inlineStr"/>
       <c r="Z61" s="2" t="inlineStr"/>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of operations into which an operation should be split. If the split method is set to 8, transferring the operation to the APP client will split it into the number of operations stated in this field. The quantities of the new operations will be equal fractions of the original quantity.</t>
-        </is>
-      </c>
+      <c r="AA61" s="2" t="inlineStr"/>
       <c r="AB61" s="2" t="inlineStr"/>
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr"/>
@@ -6444,11 +6183,7 @@
       <c r="X62" s="2" t="inlineStr"/>
       <c r="Y62" s="2" t="inlineStr"/>
       <c r="Z62" s="2" t="inlineStr"/>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the quantity used if the split method is set to 7. The operation will be split into new operations. All of the new operations will have this quantity with the exception of the last operation, which could have a different quantity. The split quantity is always stated in the product's basic U/M.</t>
-        </is>
-      </c>
+      <c r="AA62" s="2" t="inlineStr"/>
       <c r="AB62" s="2" t="inlineStr"/>
       <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr"/>
@@ -6527,13 +6262,7 @@
       <c r="X63" s="2" t="inlineStr"/>
       <c r="Y63" s="2" t="inlineStr"/>
       <c r="Z63" s="2" t="inlineStr"/>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the preparation time, which can be used to force a buffer time between operations. It is always expressed in hours with two decimal places. This time is part of the inter-operation time (which includes post-operation time, transit time and preparation time). The inter-operation time is inserted as a minimum time between the end of one operation on a manufacturing order and the start of the subsequent operation.
-The preparation time takes place during opening hours as defined by the current shift model, although it does not create any load. The preparation time entered in the routing in (PDS002) will be used in the product lead time calculation.
-The preparation time entered per order/operation in (PMS101) will be used in the MO lead time calculation.</t>
-        </is>
-      </c>
+      <c r="AA63" s="2" t="inlineStr"/>
       <c r="AB63" s="2" t="inlineStr"/>
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr"/>
@@ -6612,15 +6341,7 @@
       <c r="X64" s="2" t="inlineStr"/>
       <c r="Y64" s="2" t="inlineStr"/>
       <c r="Z64" s="2" t="inlineStr"/>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the post-operation time, which can be used to force a buffer time between operations. It is always expressed in hours with two decimal places.
-This time is part of the inter-operation time (which includes post-operation time, transit time and preparation time). The inter-operation time is inserted as a minimum time between the end of one operation in a manufacturing order and the start of the subsequent operation.
-The post-operation time always occurs when there is a capacity defined for the resource, although it does not create any load.
-The post-operation time is entered in the routing in (PDS002) and is used in the product lead time calculation.
-The post-operation time entered per order/operation (PMS101) will be used in the MO lead time calculation.</t>
-        </is>
-      </c>
+      <c r="AA64" s="2" t="inlineStr"/>
       <c r="AB64" s="2" t="inlineStr"/>
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr"/>
@@ -6707,11 +6428,7 @@
       <c r="X65" s="2" t="inlineStr"/>
       <c r="Y65" s="2" t="inlineStr"/>
       <c r="Z65" s="2" t="inlineStr"/>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the default quantity for a production lot in the work center.</t>
-        </is>
-      </c>
+      <c r="AA65" s="2" t="inlineStr"/>
       <c r="AB65" s="2" t="inlineStr"/>
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr"/>
@@ -6794,18 +6511,8 @@
       <c r="X66" s="2" t="inlineStr"/>
       <c r="Y66" s="2" t="inlineStr"/>
       <c r="Z66" s="2" t="inlineStr"/>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the operation is production lot controlled and how the lot size is determined.</t>
-        </is>
-      </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0: No
-1: Yes, and previous operation's production lot size is used for the current operation. If no quantity exists, the quantity on the current operation is used.
-2: Yes, and the production lot size from current operation is always used.</t>
-        </is>
-      </c>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr"/>
       <c r="AE66" s="2" t="inlineStr"/>
@@ -6887,17 +6594,8 @@
       <c r="X67" s="2" t="inlineStr"/>
       <c r="Y67" s="2" t="inlineStr"/>
       <c r="Z67" s="2" t="inlineStr"/>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the production lot size entered is a fixed quantity or a time-related quantity.</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>1: Quantity
-2: Hours.</t>
-        </is>
-      </c>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr"/>
       <c r="AE67" s="2" t="inlineStr"/>
@@ -6983,18 +6681,8 @@
       <c r="X68" s="2" t="inlineStr"/>
       <c r="Y68" s="2" t="inlineStr"/>
       <c r="Z68" s="2" t="inlineStr"/>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if an operation should be viewed as critical and, if so, how it should be treated. Often such an operation utilizes a bottleneck and needs to be carefully monitored during planning.</t>
-        </is>
-      </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0: Not a critical work center (default)
-1: Critical work center
-2: Critical but non-controlling.</t>
-        </is>
-      </c>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr"/>
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr"/>
       <c r="AE68" s="2" t="inlineStr"/>
@@ -7080,11 +6768,7 @@
       <c r="X69" s="2" t="inlineStr"/>
       <c r="Y69" s="2" t="inlineStr"/>
       <c r="Z69" s="2" t="inlineStr"/>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of workdays the material should be reserved before the operation's start date.</t>
-        </is>
-      </c>
+      <c r="AA69" s="2" t="inlineStr"/>
       <c r="AB69" s="2" t="inlineStr"/>
       <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr"/>
@@ -7167,14 +6851,7 @@
       <c r="X70" s="2" t="inlineStr"/>
       <c r="Y70" s="2" t="inlineStr"/>
       <c r="Z70" s="2" t="inlineStr"/>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many production days before the actual need date that the operation or material must be finished or picked.
-The shipping buffer includes subsequent operation times (in non-critical operations), waiting times, and safety times up to the start date of the next critical operation (or need date for the last operation).
-Please note that the shipping buffer is based on the standard settings in the product structure, etc. This means that any fine-tuning of the planning through, for example, M3 APS products will not affect the shipping buffer.
-The shipping buffer is normally calculated automatically but can also be manually entered in the product structure in (PDS002). The buffer is automatically calculated as the number of days between 'Original finish date this operation' and 'Original start date next operation'. Transportation time is then removed from the calculation, which is adjusted to the number of production days according to the system calendar in (CRS900) for the facility of the operation. If this is the last operation, the planning date on the macro order header in (RPS300/E) is used instead of the original start date. Please note that a manually entered shipping buffer is used without any adjustments.</t>
-        </is>
-      </c>
+      <c r="AA70" s="2" t="inlineStr"/>
       <c r="AB70" s="2" t="inlineStr"/>
       <c r="AC70" s="2" t="inlineStr"/>
       <c r="AD70" s="2" t="inlineStr"/>
@@ -7249,12 +6926,7 @@
       <c r="X71" s="2" t="inlineStr"/>
       <c r="Y71" s="2" t="inlineStr"/>
       <c r="Z71" s="2" t="inlineStr"/>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the unique identity for a formula. Together with the result identity, the formula is used by the configurator to calculate the operation's setup time.
-The formula will always give the answer in hours. This makes it possible to use the formula for different operations using different units.</t>
-        </is>
-      </c>
+      <c r="AA71" s="2" t="inlineStr"/>
       <c r="AB71" s="2" t="inlineStr"/>
       <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr"/>
@@ -7329,13 +7001,7 @@
       <c r="X72" s="2" t="inlineStr"/>
       <c r="Y72" s="2" t="inlineStr"/>
       <c r="Z72" s="2" t="inlineStr"/>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates which result ID for the specified formula is to be used to update the run time. It can only be entered in combination with the setup time formula ID.
-If only a formula ID is specified, the system will use the result last calculated in the formula.
-If either a formula or result ID is specified, the system will use the setup time specified for the operation.</t>
-        </is>
-      </c>
+      <c r="AA72" s="2" t="inlineStr"/>
       <c r="AB72" s="2" t="inlineStr"/>
       <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr"/>
@@ -7414,12 +7080,7 @@
       <c r="X73" s="2" t="inlineStr"/>
       <c r="Y73" s="2" t="inlineStr"/>
       <c r="Z73" s="2" t="inlineStr"/>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.</t>
-        </is>
-      </c>
+      <c r="AA73" s="2" t="inlineStr"/>
       <c r="AB73" s="2" t="inlineStr"/>
       <c r="AC73" s="2" t="inlineStr">
         <is>
@@ -7518,14 +7179,7 @@
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr"/>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).</t>
-        </is>
-      </c>
+      <c r="AA74" s="2" t="inlineStr"/>
       <c r="AB74" s="2" t="inlineStr"/>
       <c r="AC74" s="2" t="inlineStr">
         <is>
@@ -7636,13 +7290,7 @@
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr"/>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product number.
-For a product structure with a product structure class type of 00-'Standard' (i.e. discrete items), the product number is the same as the item number manufactured (the output from the manufacturing order) and is always used together with structures to describe what a product consists of and how it is manufactured.
-There are scenarios where each process is created as a product number on (PDS001) to serve as a placeholder for product structure class types other than 00-'Standard'. In the cases where the product structure class type is Formula product structure, Routing product structure, Bulk item product structure, Packaging material product structure, or Packaged item product structure, the Product number field is used to identify a process required for the manufacture of the ultimate product number.</t>
-        </is>
-      </c>
+      <c r="AA75" s="2" t="inlineStr"/>
       <c r="AB75" s="2" t="inlineStr"/>
       <c r="AC75" s="2" t="inlineStr">
         <is>
@@ -7745,11 +7393,7 @@
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr"/>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a product structure type. You can define more than one product structure per product and facility.</t>
-        </is>
-      </c>
+      <c r="AA76" s="2" t="inlineStr"/>
       <c r="AB76" s="2" t="inlineStr"/>
       <c r="AC76" s="2" t="inlineStr">
         <is>
@@ -7965,14 +7609,7 @@
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr"/>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates an operation number, which forms a unique ID for an operation when combined with a product number.
-For each operation number, enter the work center where the operation should be performed along with information such as operation name, run time and setup time.
-The operation number also indicates the order in which operations should be performed for a product.
-When an operation number has been entered on a material line in a product structure, it refers to the operation in which the material should first be used.</t>
-        </is>
-      </c>
+      <c r="AA78" s="2" t="inlineStr"/>
       <c r="AB78" s="2" t="inlineStr"/>
       <c r="AC78" s="2" t="inlineStr"/>
       <c r="AD78" s="2" t="inlineStr"/>
@@ -8155,12 +7792,7 @@
       <c r="X80" s="2" t="inlineStr"/>
       <c r="Y80" s="2" t="inlineStr"/>
       <c r="Z80" s="2" t="inlineStr"/>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the date when the version is valid.
-The date must not overlap with other version records. Validation is performed to ensure that conditions are met.</t>
-        </is>
-      </c>
+      <c r="AA80" s="2" t="inlineStr"/>
       <c r="AB80" s="2" t="inlineStr"/>
       <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr"/>
@@ -8251,11 +7883,7 @@
       <c r="X81" s="2" t="inlineStr"/>
       <c r="Y81" s="2" t="inlineStr"/>
       <c r="Z81" s="2" t="inlineStr"/>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates optional information indicating the drawing position corresponding to the product material line on the drawing number of the product.</t>
-        </is>
-      </c>
+      <c r="AA81" s="2" t="inlineStr"/>
       <c r="AB81" s="2" t="inlineStr"/>
       <c r="AC81" s="2" t="inlineStr"/>
       <c r="AD81" s="2" t="inlineStr"/>
@@ -8338,11 +7966,7 @@
       <c r="X82" s="2" t="inlineStr"/>
       <c r="Y82" s="2" t="inlineStr"/>
       <c r="Z82" s="2" t="inlineStr"/>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>The field is used for optional text. If the item entered does not exist in the item master table, this text may be used as the item name.</t>
-        </is>
-      </c>
+      <c r="AA82" s="2" t="inlineStr"/>
       <c r="AB82" s="2" t="inlineStr"/>
       <c r="AC82" s="2" t="inlineStr"/>
       <c r="AD82" s="2" t="inlineStr"/>
@@ -8425,11 +8049,7 @@
       <c r="X83" s="2" t="inlineStr"/>
       <c r="Y83" s="2" t="inlineStr"/>
       <c r="Z83" s="2" t="inlineStr"/>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates optional text which can be used as a technical reference.</t>
-        </is>
-      </c>
+      <c r="AA83" s="2" t="inlineStr"/>
       <c r="AB83" s="2" t="inlineStr"/>
       <c r="AC83" s="2" t="inlineStr"/>
       <c r="AD83" s="2" t="inlineStr"/>
@@ -8617,13 +8237,7 @@
       <c r="X85" s="2" t="inlineStr"/>
       <c r="Y85" s="2" t="inlineStr"/>
       <c r="Z85" s="2" t="inlineStr"/>
-      <c r="AA85" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the unit of measure that is used for an item quantity in a bill of material.
-If the product engineering U/M differs from the basic U/M, it must always be entered as an alternative U/M for the item.
-If you have defined a standard product engineering U/M, it is proposed as default, otherwise the basic U/M of the item will be used.</t>
-        </is>
-      </c>
+      <c r="AA85" s="2" t="inlineStr"/>
       <c r="AB85" s="2" t="inlineStr"/>
       <c r="AC85" s="2" t="inlineStr"/>
       <c r="AD85" s="2" t="inlineStr"/>
@@ -8710,13 +8324,7 @@
       <c r="X86" s="2" t="inlineStr"/>
       <c r="Y86" s="2" t="inlineStr"/>
       <c r="Z86" s="2" t="inlineStr"/>
-      <c r="AA86" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates one of four factors used to calculate the amount of used material. This can be used as an aid for product preparation.
-The factors used to calculate the amount are:
-The product of the factors indicates the quantity that should update the quantity used by the material record, which is only made if the product is greater than zero. Note that the factors 'Length' and 'Width' must be entered for the calculation to be made. 'Factor 1' and 'Factor 2' are used only if they are entered and greater than zero.</t>
-        </is>
-      </c>
+      <c r="AA86" s="2" t="inlineStr"/>
       <c r="AB86" s="2" t="inlineStr"/>
       <c r="AC86" s="2" t="inlineStr"/>
       <c r="AD86" s="2" t="inlineStr"/>
@@ -8799,13 +8407,7 @@
       <c r="X87" s="2" t="inlineStr"/>
       <c r="Y87" s="2" t="inlineStr"/>
       <c r="Z87" s="2" t="inlineStr"/>
-      <c r="AA87" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates one of four factors used to calculate the amount of used material. This can be used as an aid for product preparation.
-The factors used to calculate the amount are:
-The product of the factors indicates the quantity that should update the quantity used by the material record, which is only made if the product is greater than zero. Note that the factors 'Length' and 'Width' must be entered for the calculation to be made. 'Factor 1' and 'Factor 2' are used only if they are entered and greater than zero.</t>
-        </is>
-      </c>
+      <c r="AA87" s="2" t="inlineStr"/>
       <c r="AB87" s="2" t="inlineStr"/>
       <c r="AC87" s="2" t="inlineStr"/>
       <c r="AD87" s="2" t="inlineStr"/>
@@ -8892,13 +8494,7 @@
       <c r="X88" s="2" t="inlineStr"/>
       <c r="Y88" s="2" t="inlineStr"/>
       <c r="Z88" s="2" t="inlineStr"/>
-      <c r="AA88" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates one of four factors used to calculate the amount of used material. This can be used as an aid for product preparation.
-The factors used to calculate the amount are:
-The product of the factors indicates the quantity that should update the quantity used by the material record, which is only made if the product is greater than zero. Note that the factors 'Length' and 'Width' must be entered for the calculation to be made. 'Factor 1' and 'Factor 2' are used only if they are entered and greater than zero.</t>
-        </is>
-      </c>
+      <c r="AA88" s="2" t="inlineStr"/>
       <c r="AB88" s="2" t="inlineStr"/>
       <c r="AC88" s="2" t="inlineStr"/>
       <c r="AD88" s="2" t="inlineStr"/>
@@ -8985,13 +8581,7 @@
       <c r="X89" s="2" t="inlineStr"/>
       <c r="Y89" s="2" t="inlineStr"/>
       <c r="Z89" s="2" t="inlineStr"/>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates one of four factors used to calculate the amount of used material. This can be used as an aid for product preparation.
-The factors used to calculate the amount are:
-The product of the factors indicates the quantity that should update the quantity used by the material record, which is only made if the product is greater than zero. Note that the factors 'Length' and 'Width' must be entered for the calculation to be made. 'Factor 1' and 'Factor 2' are used only if they are entered and greater than zero.</t>
-        </is>
-      </c>
+      <c r="AA89" s="2" t="inlineStr"/>
       <c r="AB89" s="2" t="inlineStr"/>
       <c r="AC89" s="2" t="inlineStr"/>
       <c r="AD89" s="2" t="inlineStr"/>
@@ -9179,11 +8769,7 @@
       <c r="X91" s="2" t="inlineStr"/>
       <c r="Y91" s="2" t="inlineStr"/>
       <c r="Z91" s="2" t="inlineStr"/>
-      <c r="AA91" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the share, as a percentage, that this variant stands for in relation to the total quantity of variants entered for the product number. The information is used for requirement calculations.</t>
-        </is>
-      </c>
+      <c r="AA91" s="2" t="inlineStr"/>
       <c r="AB91" s="2" t="inlineStr"/>
       <c r="AC91" s="2" t="inlineStr"/>
       <c r="AD91" s="2" t="inlineStr"/>
@@ -9458,19 +9044,8 @@
       <c r="X94" s="2" t="inlineStr"/>
       <c r="Y94" s="2" t="inlineStr"/>
       <c r="Z94" s="2" t="inlineStr"/>
-      <c r="AA94" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the creation of stock transactions for the current item is processed if there is a connection to a subcontractor or direct purchase.</t>
-        </is>
-      </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>0: Issue performed from manufacturing order.
-1: Issue performed through general stock transactions, without possibility to override.
-2: Same as alternative 1, but the issue can be changed in the planned order.
-3: Planned purchase order is created with direct delivery from supplier to subcontractor.</t>
-        </is>
-      </c>
+      <c r="AA94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr"/>
       <c r="AC94" s="2" t="inlineStr"/>
       <c r="AD94" s="2" t="inlineStr"/>
       <c r="AE94" s="2" t="inlineStr"/>
@@ -9552,18 +9127,8 @@
       <c r="X95" s="2" t="inlineStr"/>
       <c r="Y95" s="2" t="inlineStr"/>
       <c r="Z95" s="2" t="inlineStr"/>
-      <c r="AA95" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the material line is considered a phantom item.</t>
-        </is>
-      </c>
-      <c r="AB95" s="2" t="inlineStr">
-        <is>
-          <t>Blank: Default value is used
-0: No
-1: Yes</t>
-        </is>
-      </c>
+      <c r="AA95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr"/>
       <c r="AC95" s="2" t="inlineStr"/>
       <c r="AD95" s="2" t="inlineStr"/>
       <c r="AE95" s="2" t="inlineStr"/>
@@ -9645,18 +9210,8 @@
       <c r="X96" s="2" t="inlineStr"/>
       <c r="Y96" s="2" t="inlineStr"/>
       <c r="Z96" s="2" t="inlineStr"/>
-      <c r="AA96" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether a material line should be exploded when mandatory requirements go to a lower level.</t>
-        </is>
-      </c>
-      <c r="AB96" s="2" t="inlineStr">
-        <is>
-          <t>Blank: Default value is used
-0: No
-1: Yes</t>
-        </is>
-      </c>
+      <c r="AA96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr"/>
       <c r="AC96" s="2" t="inlineStr"/>
       <c r="AD96" s="2" t="inlineStr"/>
       <c r="AE96" s="2" t="inlineStr"/>
@@ -9742,11 +9297,7 @@
       <c r="X97" s="2" t="inlineStr"/>
       <c r="Y97" s="2" t="inlineStr"/>
       <c r="Z97" s="2" t="inlineStr"/>
-      <c r="AA97" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the cost of a component if it is not entered as an item.</t>
-        </is>
-      </c>
+      <c r="AA97" s="2" t="inlineStr"/>
       <c r="AB97" s="2" t="inlineStr"/>
       <c r="AC97" s="2" t="inlineStr"/>
       <c r="AD97" s="2" t="inlineStr"/>
@@ -9833,19 +9384,8 @@
       <c r="X98" s="2" t="inlineStr"/>
       <c r="Y98" s="2" t="inlineStr"/>
       <c r="Z98" s="2" t="inlineStr"/>
-      <c r="AA98" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product type of the item.</t>
-        </is>
-      </c>
-      <c r="AB98" s="2" t="inlineStr">
-        <is>
-          <t>0: Normal item.
-1: By-product that is usable material resulting from the manufacture of another product. This is considered a standard value and is defaulted during material line entry.
-2: Co-product that results in a usable item.
-3: Main product that orders production and costing for co-products.</t>
-        </is>
-      </c>
+      <c r="AA98" s="2" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr"/>
       <c r="AC98" s="2" t="inlineStr"/>
       <c r="AD98" s="2" t="inlineStr"/>
       <c r="AE98" s="2" t="inlineStr"/>
@@ -9931,12 +9471,7 @@
       <c r="X99" s="2" t="inlineStr"/>
       <c r="Y99" s="2" t="inlineStr"/>
       <c r="Z99" s="2" t="inlineStr"/>
-      <c r="AA99" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if the material record should be included in eventual yield calculations.
-A code is entered per item to determine whether or not the automatic yield calculation should be performed.</t>
-        </is>
-      </c>
+      <c r="AA99" s="2" t="inlineStr"/>
       <c r="AB99" s="2" t="inlineStr"/>
       <c r="AC99" s="2" t="inlineStr"/>
       <c r="AD99" s="2" t="inlineStr"/>
@@ -10019,19 +9554,8 @@
       <c r="X100" s="2" t="inlineStr"/>
       <c r="Y100" s="2" t="inlineStr"/>
       <c r="Z100" s="2" t="inlineStr"/>
-      <c r="AA100" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the component should be considered as inheritance controlling for the current product.</t>
-        </is>
-      </c>
-      <c r="AB100" s="2" t="inlineStr">
-        <is>
-          <t>0: No
-1: Lot number
-2: Attribute
-3: Lot number and attribute.</t>
-        </is>
-      </c>
+      <c r="AA100" s="2" t="inlineStr"/>
+      <c r="AB100" s="2" t="inlineStr"/>
       <c r="AC100" s="2" t="inlineStr"/>
       <c r="AD100" s="2" t="inlineStr"/>
       <c r="AE100" s="2" t="inlineStr"/>
@@ -10117,14 +9641,7 @@
       <c r="X101" s="2" t="inlineStr"/>
       <c r="Y101" s="2" t="inlineStr"/>
       <c r="Z101" s="2" t="inlineStr"/>
-      <c r="AA101" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to enter standard code for each material and/or operation. The code controls whether materials and operations should be considered in estimate, requirements calculation and lead time calculation of the product, according to:
-Items that do not contain variants of materials or alternative operations normally have standard code 1 for all structure lines. Also items that contain variants of materials or operations normally have standard code 1 but combined with option percentage. Option percentage indicates how much of the materials and operations should be considered in estimate, requirements calculation and lead time calculation.
-For products with operations that are controlled by alternative routing (one 'standard' alternative routing must exists in PDS001) and record exists in PDS008, the operations will be included in the estimate, requirements and lead time calculation regardless of the option selected in this code. Otherwise, the option to include the operations in the calculation is still determined by this code.
-For products with operations that have record in PDS003, the operations will be included in the estimate, requirements and lead time calculation regardless of the option selected in this code. Otherwise, the option to include the operations in the calculation is still determined by this code.</t>
-        </is>
-      </c>
+      <c r="AA101" s="2" t="inlineStr"/>
       <c r="AB101" s="2" t="inlineStr"/>
       <c r="AC101" s="2" t="inlineStr"/>
       <c r="AD101" s="2" t="inlineStr"/>
@@ -10211,25 +9728,8 @@
       <c r="X102" s="2" t="inlineStr"/>
       <c r="Y102" s="2" t="inlineStr"/>
       <c r="Z102" s="2" t="inlineStr"/>
-      <c r="AA102" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates when and how material issues to work orders and manufacturing orders are reported.</t>
-        </is>
-      </c>
-      <c r="AB102" s="2" t="inlineStr">
-        <is>
-          <t>1: Material is issued against a picking list according to the allocation method used. Note that this method should be used if the item is order-initiated.
-2: Material is issued against a requisition and reported manually.
-3: Material is issued automatically based on the quantity reported as put away. The issue is always made from the location entered per item/warehouse.
-4: Material is issued automatically based on the quantity reported as produced in the operation where it is used. The issue is always made from the location entered per item/warehouse.
-5: Material is issued automatically based on the quantity reported as put away. The issue is made from the location entered in the work center for the operation to which the material is connected.
-6: Material is issued automatically based on the quantity that is reported as produced in the operation where it is used. The issue is made from the location specified in the work center for the operation to which the material is connected.
-7: The system sets this option to exclude the issue of the bulk item for child process orders or pack orders in (PMS060).
-8: Material is reported on one manufacturing order and issued to the next order by an external manufacturing execution system.
-9: Material is issued automatically by an external manufacturing execution system.
-0: Material issue method 0 may be used for non-stocked items for work orders in (MOS101). The material transaction status is set to 90 as soon as the transaction is finished.</t>
-        </is>
-      </c>
+      <c r="AA102" s="2" t="inlineStr"/>
+      <c r="AB102" s="2" t="inlineStr"/>
       <c r="AC102" s="2" t="inlineStr"/>
       <c r="AD102" s="2" t="inlineStr"/>
       <c r="AE102" s="2" t="inlineStr"/>
@@ -10311,12 +9811,7 @@
       <c r="X103" s="2" t="inlineStr"/>
       <c r="Y103" s="2" t="inlineStr"/>
       <c r="Z103" s="2" t="inlineStr"/>
-      <c r="AA103" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the From and To range for the revision number for which the material line is valid.
-When a revision takes place, the material line is only included if the revision number is within the entered range.</t>
-        </is>
-      </c>
+      <c r="AA103" s="2" t="inlineStr"/>
       <c r="AB103" s="2" t="inlineStr"/>
       <c r="AC103" s="2" t="inlineStr"/>
       <c r="AD103" s="2" t="inlineStr"/>
@@ -10399,12 +9894,7 @@
       <c r="X104" s="2" t="inlineStr"/>
       <c r="Y104" s="2" t="inlineStr"/>
       <c r="Z104" s="2" t="inlineStr"/>
-      <c r="AA104" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the From and To range for the revision number for which the material line is valid.
-When a revision takes place, the material line is only included if the revision number is within the entered range.</t>
-        </is>
-      </c>
+      <c r="AA104" s="2" t="inlineStr"/>
       <c r="AB104" s="2" t="inlineStr"/>
       <c r="AC104" s="2" t="inlineStr"/>
       <c r="AD104" s="2" t="inlineStr"/>
@@ -10491,11 +9981,7 @@
       <c r="X105" s="2" t="inlineStr"/>
       <c r="Y105" s="2" t="inlineStr"/>
       <c r="Z105" s="2" t="inlineStr"/>
-      <c r="AA105" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of a selection matrix or a feature used to select an item for a component line instead of the item number. After an ID is entered, this field is controlled by the component selection type and the ID is validated based on the selection type specified. If you enter a feature, it must be defined with item number as an option (parameter type 2). If you enter a matrix, it must be an item number matrix (matrix type 3).</t>
-        </is>
-      </c>
+      <c r="AA105" s="2" t="inlineStr"/>
       <c r="AB105" s="2" t="inlineStr"/>
       <c r="AC105" s="2" t="inlineStr"/>
       <c r="AD105" s="2" t="inlineStr"/>
@@ -10582,19 +10068,8 @@
       <c r="X106" s="2" t="inlineStr"/>
       <c r="Y106" s="2" t="inlineStr"/>
       <c r="Z106" s="2" t="inlineStr"/>
-      <c r="AA106" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates selection type for a component.</t>
-        </is>
-      </c>
-      <c r="AB106" s="2" t="inlineStr">
-        <is>
-          <t>0: Validation takes place according to the search hierarchy in the parameters (function key F13).
-1: The entered identity is an item number.
-2: The entered identity is a matrix.
-3: The entered identity is a feature.</t>
-        </is>
-      </c>
+      <c r="AA106" s="2" t="inlineStr"/>
+      <c r="AB106" s="2" t="inlineStr"/>
       <c r="AC106" s="2" t="inlineStr"/>
       <c r="AD106" s="2" t="inlineStr"/>
       <c r="AE106" s="2" t="inlineStr"/>
@@ -10680,17 +10155,7 @@
       <c r="X107" s="2" t="inlineStr"/>
       <c r="Y107" s="2" t="inlineStr"/>
       <c r="Z107" s="2" t="inlineStr"/>
-      <c r="AA107" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a matrix, formula or feature to close the quantity for the BoM line instead of using the quantity.
-A formula is used to calculate the quantity used, while a selection matrix is used to select the quantity used.
-A feature is used to directly determine the quantity used via the option.
-What you specify here is controlled by the field for material selection type. The ID specified is validated according to the specified selection type.
-If you specify a feature, it must be defined with numeric options (parameter type 3 or 4).
-If you specify a matrix, it must be defined to give numeric replies (matrix type 1).
-If you specify a formula, you can also enter a result ID. If you leave the result ID blank, the last result of the formula is always selected.</t>
-        </is>
-      </c>
+      <c r="AA107" s="2" t="inlineStr"/>
       <c r="AB107" s="2" t="inlineStr"/>
       <c r="AC107" s="2" t="inlineStr"/>
       <c r="AD107" s="2" t="inlineStr"/>
@@ -10777,20 +10242,8 @@
       <c r="X108" s="2" t="inlineStr"/>
       <c r="Y108" s="2" t="inlineStr"/>
       <c r="Z108" s="2" t="inlineStr"/>
-      <c r="AA108" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a selection type for quantity.</t>
-        </is>
-      </c>
-      <c r="AB108" s="2" t="inlineStr">
-        <is>
-          <t>0: Validation is performed according to the search hirerchy in the parameters (function key F13).
-1: The entered value is a quantity.
-2: The entered identity is a matrix.
-3: The entered identity is a feature.
-4: The entered identity is a formula.</t>
-        </is>
-      </c>
+      <c r="AA108" s="2" t="inlineStr"/>
+      <c r="AB108" s="2" t="inlineStr"/>
       <c r="AC108" s="2" t="inlineStr"/>
       <c r="AD108" s="2" t="inlineStr"/>
       <c r="AE108" s="2" t="inlineStr"/>
@@ -10876,11 +10329,7 @@
       <c r="X109" s="2" t="inlineStr"/>
       <c r="Y109" s="2" t="inlineStr"/>
       <c r="Z109" s="2" t="inlineStr"/>
-      <c r="AA109" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the result identity, which together with the formula identity will be used to update the quantity. If the result identity is left blank the system will use the last calculated result.</t>
-        </is>
-      </c>
+      <c r="AA109" s="2" t="inlineStr"/>
       <c r="AB109" s="2" t="inlineStr"/>
       <c r="AC109" s="2" t="inlineStr"/>
       <c r="AD109" s="2" t="inlineStr"/>
@@ -11064,12 +10513,7 @@
       <c r="X111" s="2" t="inlineStr"/>
       <c r="Y111" s="2" t="inlineStr"/>
       <c r="Z111" s="2" t="inlineStr"/>
-      <c r="AA111" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the location. A location is defined per warehouse and is thus below a warehouse in a tree structure.
-The location is part of the key identity for the balance IDs. Those are created when items are received and correspond to a combination of warehouse and location.</t>
-        </is>
-      </c>
+      <c r="AA111" s="2" t="inlineStr"/>
       <c r="AB111" s="2" t="inlineStr"/>
       <c r="AC111" s="2" t="inlineStr">
         <is>
@@ -11156,11 +10600,7 @@
       <c r="X112" s="2" t="inlineStr"/>
       <c r="Y112" s="2" t="inlineStr"/>
       <c r="Z112" s="2" t="inlineStr"/>
-      <c r="AA112" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if the material line can be affected when a manufacturing order is reported. The floor stock is included in the product costing regardless of whether this is activated or not.</t>
-        </is>
-      </c>
+      <c r="AA112" s="2" t="inlineStr"/>
       <c r="AB112" s="2" t="inlineStr"/>
       <c r="AC112" s="2" t="inlineStr"/>
       <c r="AD112" s="2" t="inlineStr"/>
@@ -11243,11 +10683,7 @@
       <c r="X113" s="2" t="inlineStr"/>
       <c r="Y113" s="2" t="inlineStr"/>
       <c r="Z113" s="2" t="inlineStr"/>
-      <c r="AA113" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the unique sequence number of an operation element.</t>
-        </is>
-      </c>
+      <c r="AA113" s="2" t="inlineStr"/>
       <c r="AB113" s="2" t="inlineStr"/>
       <c r="AC113" s="2" t="inlineStr"/>
       <c r="AD113" s="2" t="inlineStr"/>
@@ -11330,13 +10766,7 @@
       <c r="X114" s="2" t="inlineStr"/>
       <c r="Y114" s="2" t="inlineStr"/>
       <c r="Z114" s="2" t="inlineStr"/>
-      <c r="AA114" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to include the item in an available-to-promise (ATP) check in the Global CTP and in some of M3 APS planning tools.
-If you select the check box, the item is treated as a critical material. This enables you to monitor for example its ATP extra carefully during planning and confirmation of delivery dates to customer in order to avoid shortages. Examples of material that can be defined as critical, are materials with a long lead time or material that is difficult to supply.
-The supply model in (MMS059) determines whether or not an ATP check on material used is carried out when a customer order is entered.</t>
-        </is>
-      </c>
+      <c r="AA114" s="2" t="inlineStr"/>
       <c r="AB114" s="2" t="inlineStr"/>
       <c r="AC114" s="2" t="inlineStr"/>
       <c r="AD114" s="2" t="inlineStr"/>
@@ -11482,11 +10912,7 @@
       <c r="X116" s="2" t="inlineStr"/>
       <c r="Y116" s="2" t="inlineStr"/>
       <c r="Z116" s="2" t="inlineStr"/>
-      <c r="AA116" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the time of the day when material is needed.</t>
-        </is>
-      </c>
+      <c r="AA116" s="2" t="inlineStr"/>
       <c r="AB116" s="2" t="inlineStr"/>
       <c r="AC116" s="2" t="inlineStr"/>
       <c r="AD116" s="2" t="inlineStr"/>
@@ -11561,11 +10987,7 @@
       <c r="X117" s="2" t="inlineStr"/>
       <c r="Y117" s="2" t="inlineStr"/>
       <c r="Z117" s="2" t="inlineStr"/>
-      <c r="AA117" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of work days during which the material should be reserved before (â) or after (+) the start date of the operation.</t>
-        </is>
-      </c>
+      <c r="AA117" s="2" t="inlineStr"/>
       <c r="AB117" s="2" t="inlineStr"/>
       <c r="AC117" s="2" t="inlineStr"/>
       <c r="AD117" s="2" t="inlineStr"/>
@@ -11640,12 +11062,7 @@
       <c r="X118" s="2" t="inlineStr"/>
       <c r="Y118" s="2" t="inlineStr"/>
       <c r="Z118" s="2" t="inlineStr"/>
-      <c r="AA118" s="2" t="inlineStr">
-        <is>
-          <t>This check box indicates whether this particular component item will provide the quality specifications for its related manufactured item.
-If the Quality Management System (QMS) functionality is enabled, a manufactured item has components from which it may inherit quality specifications, depending on the 'Item to inherit from' check box setting on each component.</t>
-        </is>
-      </c>
+      <c r="AA118" s="2" t="inlineStr"/>
       <c r="AB118" s="2" t="inlineStr"/>
       <c r="AC118" s="2" t="inlineStr"/>
       <c r="AD118" s="2" t="inlineStr"/>
@@ -11720,20 +11137,8 @@
       <c r="X119" s="2" t="inlineStr"/>
       <c r="Y119" s="2" t="inlineStr"/>
       <c r="Z119" s="2" t="inlineStr"/>
-      <c r="AA119" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether an exchange must be performed.</t>
-        </is>
-      </c>
-      <c r="AB119" s="2" t="inlineStr">
-        <is>
-          <t>0: No
-1: Yes, removal
-2: Yes, removal and installation
-3: Yes, installation
-4: Yes, add product to work order</t>
-        </is>
-      </c>
+      <c r="AA119" s="2" t="inlineStr"/>
+      <c r="AB119" s="2" t="inlineStr"/>
       <c r="AC119" s="2" t="inlineStr"/>
       <c r="AD119" s="2" t="inlineStr"/>
       <c r="AE119" s="2" t="inlineStr"/>
@@ -11807,11 +11212,7 @@
       <c r="X120" s="2" t="inlineStr"/>
       <c r="Y120" s="2" t="inlineStr"/>
       <c r="Z120" s="2" t="inlineStr"/>
-      <c r="AA120" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if the backflush quantity should be based on the catch weight received.</t>
-        </is>
-      </c>
+      <c r="AA120" s="2" t="inlineStr"/>
       <c r="AB120" s="2" t="inlineStr"/>
       <c r="AC120" s="2" t="inlineStr"/>
       <c r="AD120" s="2" t="inlineStr"/>
@@ -11886,11 +11287,7 @@
       <c r="X121" s="2" t="inlineStr"/>
       <c r="Y121" s="2" t="inlineStr"/>
       <c r="Z121" s="2" t="inlineStr"/>
-      <c r="AA121" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the assigned line number in an external system such as a PLM system and serves as a cross-reference to the M3 line number.</t>
-        </is>
-      </c>
+      <c r="AA121" s="2" t="inlineStr"/>
       <c r="AB121" s="2" t="inlineStr"/>
       <c r="AC121" s="2" t="inlineStr"/>
       <c r="AD121" s="2" t="inlineStr"/>
@@ -11965,17 +11362,8 @@
       <c r="X122" s="2" t="inlineStr"/>
       <c r="Y122" s="2" t="inlineStr"/>
       <c r="Z122" s="2" t="inlineStr"/>
-      <c r="AA122" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the substitution table in (PDS360) should be inherited from the product in the default structure type in (CRS787).</t>
-        </is>
-      </c>
-      <c r="AB122" s="2" t="inlineStr">
-        <is>
-          <t>0: No
-1: Yes</t>
-        </is>
-      </c>
+      <c r="AA122" s="2" t="inlineStr"/>
+      <c r="AB122" s="2" t="inlineStr"/>
       <c r="AC122" s="2" t="inlineStr"/>
       <c r="AD122" s="2" t="inlineStr"/>
       <c r="AE122" s="2" t="inlineStr"/>
@@ -12049,17 +11437,8 @@
       <c r="X123" s="2" t="inlineStr"/>
       <c r="Y123" s="2" t="inlineStr"/>
       <c r="Z123" s="2" t="inlineStr"/>
-      <c r="AA123" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the manufactured material is maintained as interim stock during the MO reporting process. When the field is activated, the material can be reported as consumed in (PMS060) but yet not received in stock.</t>
-        </is>
-      </c>
-      <c r="AB123" s="2" t="inlineStr">
-        <is>
-          <t>0: No
-1: Yes</t>
-        </is>
-      </c>
+      <c r="AA123" s="2" t="inlineStr"/>
+      <c r="AB123" s="2" t="inlineStr"/>
       <c r="AC123" s="2" t="inlineStr"/>
       <c r="AD123" s="2" t="inlineStr"/>
       <c r="AE123" s="2" t="inlineStr"/>
@@ -12133,11 +11512,7 @@
       <c r="X124" s="2" t="inlineStr"/>
       <c r="Y124" s="2" t="inlineStr"/>
       <c r="Z124" s="2" t="inlineStr"/>
-      <c r="AA124" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to perform detailed backflush for manufacturing orders with 'Aggregated backflush' selected.</t>
-        </is>
-      </c>
+      <c r="AA124" s="2" t="inlineStr"/>
       <c r="AB124" s="2" t="inlineStr"/>
       <c r="AC124" s="2" t="inlineStr"/>
       <c r="AD124" s="2" t="inlineStr"/>
